--- a/Шаблон_загрузки_замеров.xlsx
+++ b/Шаблон_загрузки_замеров.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Замеры" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,27 +27,17 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font/>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -56,32 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00B0B0B0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00B0B0B0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00B0B0B0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00B0B0B0"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,33 +417,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Адрес объекта</t>
+          <t>Объект ГТС</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Район</t>
+          <t>Площадка</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Скважина (литера)</t>
+          <t>Скважина (шифр)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -498,265 +468,204 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Источник</t>
+          <t>Источник (журнал, файл)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>50 лет Октября 13</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Центральный</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Б/В/16</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Хвостохранилище ТОФ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ТОФ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3Т-1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>15.03.2026</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F2" s="2" t="n">
+      <c r="E2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Журнал мерзлотного надзора, 1 кв. 2026</t>
+      <c r="G2" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ведомость цветная ХХ ТОФ, 1 кв. 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>50 лет Октября 13</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Центральный</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Б/В/16</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Хвостохранилище ТОФ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ТОФ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3Т-1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>15.03.2026</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F3" s="2" t="n">
+      <c r="E3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>-3.15</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>50 лет Октября 13</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Центральный</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Б/В/16</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Хвостохранилище ТОФ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ТОФ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3Т-1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>15.03.2026</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F4" s="2" t="n">
+      <c r="E4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>-1.02</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>50 лет Октября 13</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Центральный</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Б/В/16</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Хвостохранилище ТОФ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ТОФ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3Т-1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>15.03.2026</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2" t="n">
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="n">
         <v>10</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>-0.85</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>50 лет Октября 13</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Центральный</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Б/В/26</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15.03.2026</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Хвостохранилище «Лебяжье» НОФ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>НОФ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ТС-12</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>ШАБЛОН ЗАГРУЗКИ ЗАМЕРОВ ТЕМПЕРАТУРЫ ГРУНТОВ — ГИС-база геотермического мониторинга зданий, г. Норильск (АНО «АНИИГБ» им. М.В. Кима)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>1. Одна строка = одна точка замера (одна глубина одной скважины на одну дату).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2. «Адрес объекта» — как в базе (допустимы варианты написания улицы); адреса вне базы отклоняются.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>3. «Район»: Центральный / Талнах / Кайеркан (справочно).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>4. «Скважина (литера)» — например Б/В/16; если литеры нет, оставьте пустым.</t>
+      <c r="G6" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Журнал определения температур, Лебяжье</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>5. «Дата замера» — ДД.ММ.ГГГГ или ГГГГ-ММ-ДД.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>6. Глубины — в метрах от поверхности; температура — в °C со знаком «минус» для отрицательных.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>7. Строки с примерами (2–6) перед загрузкой удалить.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>8. Загрузка: кнопка «⬆ Загрузка данных» в шапке ГИС-базы → «Выбрать файл».</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Структура ведомости соответствует ГОСТ 25358-2020 (прил. В, Д); журнал мерзлотного надзора — ВСН 01-89, СП 25.13330.2020.</t>
-        </is>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Хвостохранилище «Лебяжье» НОФ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>НОФ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ТС-12</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.1</v>
       </c>
     </row>
   </sheetData>
